--- a/artfynd/A 44562-2023 artfynd.xlsx
+++ b/artfynd/A 44562-2023 artfynd.xlsx
@@ -889,45 +889,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125717418</v>
+        <v>125716916</v>
       </c>
       <c r="B4" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397535</v>
+        <v>397714</v>
       </c>
       <c r="R4" t="n">
-        <v>6697591</v>
+        <v>6697653</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,54 +995,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125716916</v>
+        <v>125717418</v>
       </c>
       <c r="B5" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397714</v>
+        <v>397535</v>
       </c>
       <c r="R5" t="n">
-        <v>6697653</v>
+        <v>6697591</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1791,32 +1791,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125717136</v>
+        <v>125717272</v>
       </c>
       <c r="B13" t="n">
-        <v>78967</v>
+        <v>75005</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>397700</v>
+        <v>397690</v>
       </c>
       <c r="R13" t="n">
-        <v>6697645</v>
+        <v>6697624</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1888,32 +1888,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125717272</v>
+        <v>125716981</v>
       </c>
       <c r="B14" t="n">
-        <v>75005</v>
+        <v>79585</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>397690</v>
+        <v>397721</v>
       </c>
       <c r="R14" t="n">
-        <v>6697624</v>
+        <v>6697643</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,10 +1985,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125716981</v>
+        <v>125717136</v>
       </c>
       <c r="B15" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1996,21 +1996,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>397721</v>
+        <v>397700</v>
       </c>
       <c r="R15" t="n">
-        <v>6697643</v>
+        <v>6697645</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2082,32 +2082,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125717445</v>
+        <v>125717091</v>
       </c>
       <c r="B16" t="n">
-        <v>78967</v>
+        <v>75005</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>397573</v>
+        <v>397710</v>
       </c>
       <c r="R16" t="n">
-        <v>6697618</v>
+        <v>6697623</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2150,19 +2150,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>16:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2177,44 +2167,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125717091</v>
+        <v>125717445</v>
       </c>
       <c r="B17" t="n">
-        <v>75005</v>
+        <v>78967</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2224,13 +2214,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>397710</v>
+        <v>397573</v>
       </c>
       <c r="R17" t="n">
-        <v>6697623</v>
+        <v>6697618</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2257,9 +2247,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2274,12 +2274,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 44562-2023 artfynd.xlsx
+++ b/artfynd/A 44562-2023 artfynd.xlsx
@@ -1791,32 +1791,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125717272</v>
+        <v>125717136</v>
       </c>
       <c r="B13" t="n">
-        <v>75005</v>
+        <v>78967</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>397690</v>
+        <v>397700</v>
       </c>
       <c r="R13" t="n">
-        <v>6697624</v>
+        <v>6697645</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1888,32 +1888,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125716981</v>
+        <v>125717272</v>
       </c>
       <c r="B14" t="n">
-        <v>79585</v>
+        <v>75005</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>397721</v>
+        <v>397690</v>
       </c>
       <c r="R14" t="n">
-        <v>6697643</v>
+        <v>6697624</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,10 +1985,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125717136</v>
+        <v>125716981</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1996,21 +1996,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>397700</v>
+        <v>397721</v>
       </c>
       <c r="R15" t="n">
-        <v>6697645</v>
+        <v>6697643</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 44562-2023 artfynd.xlsx
+++ b/artfynd/A 44562-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125717695</v>
       </c>
       <c r="B2" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>125717687</v>
       </c>
       <c r="B3" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,54 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125716916</v>
+        <v>125717418</v>
       </c>
       <c r="B4" t="n">
-        <v>98331</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397714</v>
+        <v>397535</v>
       </c>
       <c r="R4" t="n">
-        <v>6697653</v>
+        <v>6697591</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,45 +986,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125717418</v>
+        <v>125716916</v>
       </c>
       <c r="B5" t="n">
-        <v>78967</v>
+        <v>98334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397535</v>
+        <v>397714</v>
       </c>
       <c r="R5" t="n">
-        <v>6697591</v>
+        <v>6697653</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1095,7 @@
         <v>125716948</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>125717498</v>
       </c>
       <c r="B7" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>125717537</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>125717182</v>
       </c>
       <c r="B9" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>125717115</v>
       </c>
       <c r="B10" t="n">
-        <v>75005</v>
+        <v>75006</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>125717234</v>
       </c>
       <c r="B11" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>125717018</v>
       </c>
       <c r="B12" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,32 +1791,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125717136</v>
+        <v>125717272</v>
       </c>
       <c r="B13" t="n">
-        <v>78967</v>
+        <v>75006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>397700</v>
+        <v>397690</v>
       </c>
       <c r="R13" t="n">
-        <v>6697645</v>
+        <v>6697624</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1888,32 +1888,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125717272</v>
+        <v>125716981</v>
       </c>
       <c r="B14" t="n">
-        <v>75005</v>
+        <v>79586</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>397690</v>
+        <v>397721</v>
       </c>
       <c r="R14" t="n">
-        <v>6697624</v>
+        <v>6697643</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,10 +1985,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125716981</v>
+        <v>125717136</v>
       </c>
       <c r="B15" t="n">
-        <v>79585</v>
+        <v>78968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1996,21 +1996,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>397721</v>
+        <v>397700</v>
       </c>
       <c r="R15" t="n">
-        <v>6697643</v>
+        <v>6697645</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2085,7 +2085,7 @@
         <v>125717091</v>
       </c>
       <c r="B16" t="n">
-        <v>75005</v>
+        <v>75006</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>125717445</v>
       </c>
       <c r="B17" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>125717696</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 44562-2023 artfynd.xlsx
+++ b/artfynd/A 44562-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125717695</v>
       </c>
       <c r="B2" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,48 +782,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125717687</v>
+        <v>125716916</v>
       </c>
       <c r="B3" t="n">
-        <v>78726</v>
+        <v>98338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397545</v>
+        <v>397714</v>
       </c>
       <c r="R3" t="n">
-        <v>6697588</v>
+        <v>6697653</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,19 +859,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:41</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +876,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125717418</v>
+        <v>125717687</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>78730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +923,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397535</v>
+        <v>397545</v>
       </c>
       <c r="R4" t="n">
-        <v>6697591</v>
+        <v>6697588</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,9 +956,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,66 +983,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125716916</v>
+        <v>125717418</v>
       </c>
       <c r="B5" t="n">
-        <v>98334</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397714</v>
+        <v>397535</v>
       </c>
       <c r="R5" t="n">
-        <v>6697653</v>
+        <v>6697591</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1095,7 @@
         <v>125716948</v>
       </c>
       <c r="B6" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>125717498</v>
       </c>
       <c r="B7" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>125717537</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>125717182</v>
       </c>
       <c r="B9" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>125717234</v>
       </c>
       <c r="B11" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>125717018</v>
       </c>
       <c r="B12" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>125716981</v>
       </c>
       <c r="B14" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>125717136</v>
       </c>
       <c r="B15" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>125717445</v>
       </c>
       <c r="B17" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>125717696</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 44562-2023 artfynd.xlsx
+++ b/artfynd/A 44562-2023 artfynd.xlsx
@@ -1791,32 +1791,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125717272</v>
+        <v>125717136</v>
       </c>
       <c r="B13" t="n">
-        <v>75006</v>
+        <v>78972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>397690</v>
+        <v>397700</v>
       </c>
       <c r="R13" t="n">
-        <v>6697624</v>
+        <v>6697645</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1888,32 +1888,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125716981</v>
+        <v>125717272</v>
       </c>
       <c r="B14" t="n">
-        <v>79590</v>
+        <v>75006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>397721</v>
+        <v>397690</v>
       </c>
       <c r="R14" t="n">
-        <v>6697643</v>
+        <v>6697624</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,10 +1985,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125717136</v>
+        <v>125716981</v>
       </c>
       <c r="B15" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1996,21 +1996,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>397700</v>
+        <v>397721</v>
       </c>
       <c r="R15" t="n">
-        <v>6697645</v>
+        <v>6697643</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 44562-2023 artfynd.xlsx
+++ b/artfynd/A 44562-2023 artfynd.xlsx
@@ -782,57 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125716916</v>
+        <v>125717687</v>
       </c>
       <c r="B3" t="n">
-        <v>98338</v>
+        <v>78730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397714</v>
+        <v>397545</v>
       </c>
       <c r="R3" t="n">
-        <v>6697653</v>
+        <v>6697588</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,9 +850,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125717687</v>
+        <v>125717418</v>
       </c>
       <c r="B4" t="n">
-        <v>78730</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397545</v>
+        <v>397535</v>
       </c>
       <c r="R4" t="n">
-        <v>6697588</v>
+        <v>6697591</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -956,19 +957,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:41</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,57 +974,66 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125717418</v>
+        <v>125716916</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397535</v>
+        <v>397714</v>
       </c>
       <c r="R5" t="n">
-        <v>6697591</v>
+        <v>6697653</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 44562-2023 artfynd.xlsx
+++ b/artfynd/A 44562-2023 artfynd.xlsx
@@ -782,48 +782,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125717687</v>
+        <v>125716916</v>
       </c>
       <c r="B3" t="n">
-        <v>78730</v>
+        <v>98339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397545</v>
+        <v>397714</v>
       </c>
       <c r="R3" t="n">
-        <v>6697588</v>
+        <v>6697653</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,19 +859,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:41</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +876,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125717418</v>
+        <v>125717687</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>78730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +923,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397535</v>
+        <v>397545</v>
       </c>
       <c r="R4" t="n">
-        <v>6697591</v>
+        <v>6697588</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,9 +956,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,66 +983,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125716916</v>
+        <v>125717418</v>
       </c>
       <c r="B5" t="n">
-        <v>98339</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397714</v>
+        <v>397535</v>
       </c>
       <c r="R5" t="n">
-        <v>6697653</v>
+        <v>6697591</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 44562-2023 artfynd.xlsx
+++ b/artfynd/A 44562-2023 artfynd.xlsx
@@ -782,54 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125716916</v>
+        <v>125717418</v>
       </c>
       <c r="B3" t="n">
-        <v>98339</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397714</v>
+        <v>397535</v>
       </c>
       <c r="R3" t="n">
-        <v>6697653</v>
+        <v>6697591</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,48 +879,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125717687</v>
+        <v>125716916</v>
       </c>
       <c r="B4" t="n">
-        <v>78730</v>
+        <v>98339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397545</v>
+        <v>397714</v>
       </c>
       <c r="R4" t="n">
-        <v>6697588</v>
+        <v>6697653</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -956,19 +956,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:41</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,22 +973,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125717418</v>
+        <v>125717687</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>78730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,21 +996,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,13 +1020,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397535</v>
+        <v>397545</v>
       </c>
       <c r="R5" t="n">
-        <v>6697591</v>
+        <v>6697588</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,9 +1053,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1080,12 +1080,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 44562-2023 artfynd.xlsx
+++ b/artfynd/A 44562-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125717695</v>
       </c>
       <c r="B2" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125717418</v>
+        <v>125717687</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397535</v>
+        <v>397545</v>
       </c>
       <c r="R3" t="n">
-        <v>6697591</v>
+        <v>6697588</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,9 +850,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,66 +877,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125716916</v>
+        <v>125717418</v>
       </c>
       <c r="B4" t="n">
-        <v>98339</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397714</v>
+        <v>397535</v>
       </c>
       <c r="R4" t="n">
-        <v>6697653</v>
+        <v>6697591</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,48 +986,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125717687</v>
+        <v>125716916</v>
       </c>
       <c r="B5" t="n">
-        <v>78730</v>
+        <v>98341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397545</v>
+        <v>397714</v>
       </c>
       <c r="R5" t="n">
-        <v>6697588</v>
+        <v>6697653</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1053,19 +1063,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:41</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1080,12 +1080,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
         <v>125716948</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>125717498</v>
       </c>
       <c r="B7" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>125717537</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>125717182</v>
       </c>
       <c r="B9" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>125717115</v>
       </c>
       <c r="B10" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>125717234</v>
       </c>
       <c r="B11" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>125717018</v>
       </c>
       <c r="B12" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,10 +1791,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125717136</v>
+        <v>125716981</v>
       </c>
       <c r="B13" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1802,21 +1802,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>397700</v>
+        <v>397721</v>
       </c>
       <c r="R13" t="n">
-        <v>6697645</v>
+        <v>6697643</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1891,7 +1891,7 @@
         <v>125717272</v>
       </c>
       <c r="B14" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,10 +1985,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125716981</v>
+        <v>125717136</v>
       </c>
       <c r="B15" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1996,21 +1996,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>397721</v>
+        <v>397700</v>
       </c>
       <c r="R15" t="n">
-        <v>6697643</v>
+        <v>6697645</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2085,7 +2085,7 @@
         <v>125717091</v>
       </c>
       <c r="B16" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>125717445</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>125717696</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 44562-2023 artfynd.xlsx
+++ b/artfynd/A 44562-2023 artfynd.xlsx
@@ -782,48 +782,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125717687</v>
+        <v>125716916</v>
       </c>
       <c r="B3" t="n">
-        <v>78731</v>
+        <v>98341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397545</v>
+        <v>397714</v>
       </c>
       <c r="R3" t="n">
-        <v>6697588</v>
+        <v>6697653</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,19 +859,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:41</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +876,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125717418</v>
+        <v>125717687</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +923,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397535</v>
+        <v>397545</v>
       </c>
       <c r="R4" t="n">
-        <v>6697591</v>
+        <v>6697588</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,9 +956,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,66 +983,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125716916</v>
+        <v>125717418</v>
       </c>
       <c r="B5" t="n">
-        <v>98341</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397714</v>
+        <v>397535</v>
       </c>
       <c r="R5" t="n">
-        <v>6697653</v>
+        <v>6697591</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1791,10 +1791,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125716981</v>
+        <v>125717136</v>
       </c>
       <c r="B13" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1802,21 +1802,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>397721</v>
+        <v>397700</v>
       </c>
       <c r="R13" t="n">
-        <v>6697643</v>
+        <v>6697645</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1888,32 +1888,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125717272</v>
+        <v>125716981</v>
       </c>
       <c r="B14" t="n">
-        <v>75007</v>
+        <v>79591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>397690</v>
+        <v>397721</v>
       </c>
       <c r="R14" t="n">
-        <v>6697624</v>
+        <v>6697643</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,32 +1985,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125717136</v>
+        <v>125717272</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>75007</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>397700</v>
+        <v>397690</v>
       </c>
       <c r="R15" t="n">
-        <v>6697645</v>
+        <v>6697624</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 44562-2023 artfynd.xlsx
+++ b/artfynd/A 44562-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>125716916</v>
       </c>
       <c r="B3" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1791,32 +1791,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125717136</v>
+        <v>125717272</v>
       </c>
       <c r="B13" t="n">
-        <v>78973</v>
+        <v>75007</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>397700</v>
+        <v>397690</v>
       </c>
       <c r="R13" t="n">
-        <v>6697645</v>
+        <v>6697624</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1888,10 +1888,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125716981</v>
+        <v>125717136</v>
       </c>
       <c r="B14" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1899,21 +1899,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>397721</v>
+        <v>397700</v>
       </c>
       <c r="R14" t="n">
-        <v>6697643</v>
+        <v>6697645</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,32 +1985,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125717272</v>
+        <v>125716981</v>
       </c>
       <c r="B15" t="n">
-        <v>75007</v>
+        <v>79591</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>397690</v>
+        <v>397721</v>
       </c>
       <c r="R15" t="n">
-        <v>6697624</v>
+        <v>6697643</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2082,32 +2082,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125717091</v>
+        <v>125717445</v>
       </c>
       <c r="B16" t="n">
-        <v>75007</v>
+        <v>78973</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>397710</v>
+        <v>397573</v>
       </c>
       <c r="R16" t="n">
-        <v>6697623</v>
+        <v>6697618</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2150,9 +2150,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2167,44 +2177,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125717445</v>
+        <v>125717091</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>75007</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2214,13 +2224,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>397573</v>
+        <v>397710</v>
       </c>
       <c r="R17" t="n">
-        <v>6697618</v>
+        <v>6697623</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2247,19 +2257,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2274,12 +2274,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 44562-2023 artfynd.xlsx
+++ b/artfynd/A 44562-2023 artfynd.xlsx
@@ -782,54 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125716916</v>
+        <v>125717418</v>
       </c>
       <c r="B3" t="n">
-        <v>98343</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397714</v>
+        <v>397535</v>
       </c>
       <c r="R3" t="n">
-        <v>6697653</v>
+        <v>6697591</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -995,45 +986,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125717418</v>
+        <v>125716916</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>98345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397535</v>
+        <v>397714</v>
       </c>
       <c r="R5" t="n">
-        <v>6697591</v>
+        <v>6697653</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125716948</v>
+        <v>125717537</v>
       </c>
       <c r="B6" t="n">
         <v>78973</v>
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>397724</v>
+        <v>397534</v>
       </c>
       <c r="R6" t="n">
-        <v>6697658</v>
+        <v>6697644</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1160,9 +1160,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1177,12 +1187,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1296,7 +1306,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125717537</v>
+        <v>125716948</v>
       </c>
       <c r="B8" t="n">
         <v>78973</v>
@@ -1331,13 +1341,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>397534</v>
+        <v>397724</v>
       </c>
       <c r="R8" t="n">
-        <v>6697644</v>
+        <v>6697658</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1364,19 +1374,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1391,12 +1391,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1888,10 +1888,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125717136</v>
+        <v>125716981</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1899,21 +1899,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>397700</v>
+        <v>397721</v>
       </c>
       <c r="R14" t="n">
-        <v>6697645</v>
+        <v>6697643</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,10 +1985,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125716981</v>
+        <v>125717136</v>
       </c>
       <c r="B15" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1996,21 +1996,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>397721</v>
+        <v>397700</v>
       </c>
       <c r="R15" t="n">
-        <v>6697643</v>
+        <v>6697645</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 44562-2023 artfynd.xlsx
+++ b/artfynd/A 44562-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125717695</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>125717418</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125717687</v>
       </c>
       <c r="B4" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>125716916</v>
       </c>
       <c r="B5" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125717537</v>
+        <v>125716948</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>397534</v>
+        <v>397724</v>
       </c>
       <c r="R6" t="n">
-        <v>6697644</v>
+        <v>6697658</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1160,19 +1160,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1187,12 +1177,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1202,7 +1192,7 @@
         <v>125717498</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125716948</v>
+        <v>125717537</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,13 +1331,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>397724</v>
+        <v>397534</v>
       </c>
       <c r="R8" t="n">
-        <v>6697658</v>
+        <v>6697644</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1374,9 +1364,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1391,12 +1391,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1406,7 +1406,7 @@
         <v>125717182</v>
       </c>
       <c r="B9" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>125717115</v>
       </c>
       <c r="B10" t="n">
-        <v>75007</v>
+        <v>75011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>125717234</v>
       </c>
       <c r="B11" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>125717018</v>
       </c>
       <c r="B12" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>125717272</v>
       </c>
       <c r="B13" t="n">
-        <v>75007</v>
+        <v>75011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,10 +1888,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125716981</v>
+        <v>125717136</v>
       </c>
       <c r="B14" t="n">
-        <v>79591</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1899,21 +1899,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>397721</v>
+        <v>397700</v>
       </c>
       <c r="R14" t="n">
-        <v>6697643</v>
+        <v>6697645</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,10 +1985,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125717136</v>
+        <v>125716981</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>79595</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1996,21 +1996,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>397700</v>
+        <v>397721</v>
       </c>
       <c r="R15" t="n">
-        <v>6697645</v>
+        <v>6697643</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2085,7 +2085,7 @@
         <v>125717445</v>
       </c>
       <c r="B16" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>125717091</v>
       </c>
       <c r="B17" t="n">
-        <v>75007</v>
+        <v>75011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>125717696</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 44562-2023 artfynd.xlsx
+++ b/artfynd/A 44562-2023 artfynd.xlsx
@@ -782,45 +782,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125717418</v>
+        <v>125716916</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>98349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397535</v>
+        <v>397714</v>
       </c>
       <c r="R3" t="n">
-        <v>6697591</v>
+        <v>6697653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125717687</v>
+        <v>125717418</v>
       </c>
       <c r="B4" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,13 +923,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397545</v>
+        <v>397535</v>
       </c>
       <c r="R4" t="n">
-        <v>6697588</v>
+        <v>6697591</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -947,19 +956,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:41</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,69 +973,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125716916</v>
+        <v>125717687</v>
       </c>
       <c r="B5" t="n">
-        <v>98349</v>
+        <v>78735</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397714</v>
+        <v>397545</v>
       </c>
       <c r="R5" t="n">
-        <v>6697653</v>
+        <v>6697588</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,9 +1053,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1080,12 +1080,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 44562-2023 artfynd.xlsx
+++ b/artfynd/A 44562-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>125716916</v>
       </c>
       <c r="B3" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125717418</v>
+        <v>125717687</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,13 +923,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397535</v>
+        <v>397545</v>
       </c>
       <c r="R4" t="n">
-        <v>6697591</v>
+        <v>6697588</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -956,9 +956,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -973,22 +983,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125717687</v>
+        <v>125717418</v>
       </c>
       <c r="B5" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1020,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397545</v>
+        <v>397535</v>
       </c>
       <c r="R5" t="n">
-        <v>6697588</v>
+        <v>6697591</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1053,19 +1063,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:41</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1080,12 +1080,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 44562-2023 artfynd.xlsx
+++ b/artfynd/A 44562-2023 artfynd.xlsx
@@ -782,57 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125716916</v>
+        <v>125717687</v>
       </c>
       <c r="B3" t="n">
-        <v>98352</v>
+        <v>78735</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397714</v>
+        <v>397545</v>
       </c>
       <c r="R3" t="n">
-        <v>6697653</v>
+        <v>6697588</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,9 +850,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125717687</v>
+        <v>125717418</v>
       </c>
       <c r="B4" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397545</v>
+        <v>397535</v>
       </c>
       <c r="R4" t="n">
-        <v>6697588</v>
+        <v>6697591</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -956,19 +957,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:41</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,57 +974,66 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125717418</v>
+        <v>125716916</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397535</v>
+        <v>397714</v>
       </c>
       <c r="R5" t="n">
-        <v>6697591</v>
+        <v>6697653</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 44562-2023 artfynd.xlsx
+++ b/artfynd/A 44562-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2391,6 +2391,218 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125717574</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91506</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>65</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fläckporing</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Anthoporia albobrunnea</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>lövåsmyren väst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>397525</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6697588</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126501652</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78647</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>353</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>lövåsmyren väst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>397525</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6697588</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44562-2023 artfynd.xlsx
+++ b/artfynd/A 44562-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2603,6 +2603,103 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132894715</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kristinefors, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>397584</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6697617</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson, Isabel Hedén, David Schinkler, Julia Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44562-2023 artfynd.xlsx
+++ b/artfynd/A 44562-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125717695</v>
+        <v>125717574</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>lövåsmyren väst, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>397536</v>
+        <v>397525</v>
       </c>
       <c r="R2" t="n">
-        <v>6697643</v>
+        <v>6697588</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,49 +746,50 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:50</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:50</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125717687</v>
+        <v>125717791</v>
       </c>
       <c r="B3" t="n">
-        <v>78735</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +821,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397545</v>
+        <v>397585</v>
       </c>
       <c r="R3" t="n">
-        <v>6697588</v>
+        <v>6697687</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,19 +854,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:41</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +871,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125717418</v>
+        <v>125717500</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +894,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397535</v>
+        <v>397511</v>
       </c>
       <c r="R4" t="n">
-        <v>6697591</v>
+        <v>6697571</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,54 +980,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125716916</v>
+        <v>126501652</v>
       </c>
       <c r="B5" t="n">
-        <v>98352</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>lövåsmyren väst, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397714</v>
+        <v>397525</v>
       </c>
       <c r="R5" t="n">
-        <v>6697653</v>
+        <v>6697588</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,6 +1062,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1092,10 +1081,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125716948</v>
+        <v>322748</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,37 +1092,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>LÖVÅSMYREN VÄSTRA (13D0a03), Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>397724</v>
+        <v>397705</v>
       </c>
       <c r="R6" t="n">
-        <v>6697658</v>
+        <v>6697631</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,12 +1146,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>1996-06-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>1996-06-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>130300031 / PHE FERF / Enstaka-sparsam (1)  / MAJ / OBJ.AREA:0,6 ha</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,30 +1167,44 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrskog /</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Låga av gran</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Via Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125717498</v>
+        <v>120667563</v>
       </c>
       <c r="B7" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1220,17 +1228,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>397576</v>
+        <v>397512</v>
       </c>
       <c r="R7" t="n">
-        <v>6697616</v>
+        <v>6697672</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1254,22 +1262,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1284,26 +1292,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Malin Max Nordgren, Kaiko Gustafsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125717537</v>
+        <v>120667733</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1327,17 +1335,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>397534</v>
+        <v>397560</v>
       </c>
       <c r="R8" t="n">
-        <v>6697644</v>
+        <v>6697669</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1361,22 +1369,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1391,57 +1399,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125717182</v>
+        <v>120668086</v>
       </c>
       <c r="B9" t="n">
-        <v>78736</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>397698</v>
+        <v>397665</v>
       </c>
       <c r="R9" t="n">
-        <v>6697630</v>
+        <v>6697689</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,12 +1476,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1488,44 +1506,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125717115</v>
+        <v>125716840</v>
       </c>
       <c r="B10" t="n">
-        <v>75011</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>397700</v>
+        <v>397730</v>
       </c>
       <c r="R10" t="n">
-        <v>6697621</v>
+        <v>6697688</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,32 +1615,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125717234</v>
+        <v>125716948</v>
       </c>
       <c r="B11" t="n">
-        <v>78735</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1632,10 +1650,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>397698</v>
+        <v>397724</v>
       </c>
       <c r="R11" t="n">
-        <v>6697630</v>
+        <v>6697658</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1697,11 +1715,11 @@
         <v>125717018</v>
       </c>
       <c r="B12" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1791,32 +1809,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125717272</v>
+        <v>125717136</v>
       </c>
       <c r="B13" t="n">
-        <v>75011</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,10 +1844,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>397690</v>
+        <v>397700</v>
       </c>
       <c r="R13" t="n">
-        <v>6697624</v>
+        <v>6697645</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1888,14 +1906,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125717136</v>
+        <v>125717418</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1923,10 +1941,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>397700</v>
+        <v>397535</v>
       </c>
       <c r="R14" t="n">
-        <v>6697645</v>
+        <v>6697591</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,32 +2003,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125716981</v>
+        <v>125717445</v>
       </c>
       <c r="B15" t="n">
-        <v>79595</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2020,13 +2038,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>397721</v>
+        <v>397573</v>
       </c>
       <c r="R15" t="n">
-        <v>6697643</v>
+        <v>6697618</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2053,9 +2071,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2070,26 +2098,26 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125717445</v>
+        <v>125717446</v>
       </c>
       <c r="B16" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2117,13 +2145,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>397573</v>
+        <v>397545</v>
       </c>
       <c r="R16" t="n">
-        <v>6697618</v>
+        <v>6697577</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2150,19 +2178,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>16:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2177,44 +2195,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125717091</v>
+        <v>125717696</v>
       </c>
       <c r="B17" t="n">
-        <v>75011</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2224,13 +2242,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>397710</v>
+        <v>397545</v>
       </c>
       <c r="R17" t="n">
-        <v>6697623</v>
+        <v>6697588</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2257,9 +2275,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2274,26 +2302,26 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125717696</v>
+        <v>125717498</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2321,13 +2349,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>397545</v>
+        <v>397576</v>
       </c>
       <c r="R18" t="n">
-        <v>6697588</v>
+        <v>6697616</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2356,7 +2384,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2366,7 +2394,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2381,22 +2409,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125717574</v>
+        <v>125717537</v>
       </c>
       <c r="B19" t="n">
-        <v>91506</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2404,40 +2432,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>lövåsmyren väst, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>397525</v>
+        <v>397534</v>
       </c>
       <c r="R19" t="n">
-        <v>6697588</v>
+        <v>6697644</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2464,91 +2489,87 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126501652</v>
+        <v>125717568</v>
       </c>
       <c r="B20" t="n">
-        <v>78647</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>lövåsmyren väst, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>397525</v>
+        <v>397536</v>
       </c>
       <c r="R20" t="n">
-        <v>6697588</v>
+        <v>6697643</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2575,78 +2596,87 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132894715</v>
+        <v>125717633</v>
       </c>
       <c r="B21" t="n">
-        <v>57145</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kristinefors, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>397584</v>
+        <v>397513</v>
       </c>
       <c r="R21" t="n">
-        <v>6697617</v>
+        <v>6697565</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2670,12 +2700,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2690,15 +2720,1237 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125717768</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>397538</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6697682</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125717848</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>397549</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6697680</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125717091</v>
+      </c>
+      <c r="B24" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>397710</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6697623</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125717115</v>
+      </c>
+      <c r="B25" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>397700</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6697621</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125717272</v>
+      </c>
+      <c r="B26" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>397690</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6697624</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1988470</v>
+      </c>
+      <c r="B27" t="n">
+        <v>75300</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>LÖVÅSMYREN VÄSTRA (13D0a03), Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>397705</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6697631</v>
+      </c>
+      <c r="S27" t="n">
+        <v>50</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>1996-06-07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>1996-06-07</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>130300031 / ART VINO / Enstaka-sparsam (1)  / MAJ / OBJ.AREA:0,6 ha</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Barrskog /</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Gammalt lövträd</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Via Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125717234</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>397698</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6697630</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125717687</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>397545</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6697588</v>
+      </c>
+      <c r="S29" t="n">
+        <v>8</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125716981</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>397721</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6697643</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132894715</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kristinefors, Vrm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>397584</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6697617</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
           <t>Joakim Karlsson</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
+      <c r="AX31" t="inlineStr">
         <is>
           <t>Joakim Karlsson, Isabel Hedén, David Schinkler, Julia Dahlberg</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125716916</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>397714</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6697653</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125717182</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>397698</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6697630</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44562-2023 artfynd.xlsx
+++ b/artfynd/A 44562-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125717574</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125717791</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125717500</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126501652</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1194,6 +1219,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/322748</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1301,6 +1331,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120667563</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1408,6 +1443,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120667733</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1515,6 +1555,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120668086</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1612,6 +1657,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125716840</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1709,6 +1759,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125716948</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1806,6 +1861,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125717018</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1903,6 +1963,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125717136</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2000,6 +2065,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125717418</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2107,6 +2177,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125717445</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2204,6 +2279,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125717446</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2311,6 +2391,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125717696</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2418,6 +2503,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125717498</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2525,6 +2615,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125717537</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2632,6 +2727,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125717568</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2729,6 +2829,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125717633</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2836,6 +2941,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125717768</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2943,6 +3053,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125717848</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3040,6 +3155,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125717091</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3137,6 +3257,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125717115</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3234,6 +3359,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125717272</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3350,6 +3480,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1988470</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3447,6 +3582,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125717234</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3554,6 +3694,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125717687</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3651,6 +3796,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125716981</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3748,6 +3898,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132894715</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3854,6 +4009,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125716916</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3951,8 +4111,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125717182</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>